--- a/data/nzd0540/nzd0540.xlsx
+++ b/data/nzd0540/nzd0540.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O503"/>
+  <dimension ref="A1:O504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26091,6 +26091,57 @@
       <c r="O503" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>253.96</v>
+      </c>
+      <c r="C504" t="n">
+        <v>284.52</v>
+      </c>
+      <c r="D504" t="n">
+        <v>297.3</v>
+      </c>
+      <c r="E504" t="n">
+        <v>297.6</v>
+      </c>
+      <c r="F504" t="n">
+        <v>298.21</v>
+      </c>
+      <c r="G504" t="n">
+        <v>302.36</v>
+      </c>
+      <c r="H504" t="n">
+        <v>287.23</v>
+      </c>
+      <c r="I504" t="n">
+        <v>288.2</v>
+      </c>
+      <c r="J504" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="K504" t="n">
+        <v>299.76</v>
+      </c>
+      <c r="L504" t="n">
+        <v>296.69</v>
+      </c>
+      <c r="M504" t="n">
+        <v>291.11</v>
+      </c>
+      <c r="N504" t="n">
+        <v>295.51</v>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26105,7 +26156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31238,6 +31289,16 @@
       </c>
       <c r="B513" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>
@@ -31406,28 +31467,28 @@
         <v>0.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2029268408319183</v>
+        <v>0.1900977060008421</v>
       </c>
       <c r="J2" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K2" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002786095470556305</v>
+        <v>0.002449896557775055</v>
       </c>
       <c r="M2" t="n">
-        <v>20.71002532712754</v>
+        <v>20.7329468995554</v>
       </c>
       <c r="N2" t="n">
-        <v>772.4932280070223</v>
+        <v>772.9538256445893</v>
       </c>
       <c r="O2" t="n">
-        <v>27.79376239387216</v>
+        <v>27.80204714844914</v>
       </c>
       <c r="P2" t="n">
-        <v>280.4074702489409</v>
+        <v>280.543616608214</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31488,28 +31549,28 @@
         <v>0.0368</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2258009141166176</v>
+        <v>-0.2290225642571355</v>
       </c>
       <c r="J3" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K3" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01382792593504323</v>
+        <v>0.01427037193351222</v>
       </c>
       <c r="M3" t="n">
-        <v>10.87922608634554</v>
+        <v>10.8760469825422</v>
       </c>
       <c r="N3" t="n">
-        <v>193.0626961486976</v>
+        <v>192.8076862151424</v>
       </c>
       <c r="O3" t="n">
-        <v>13.89470028999178</v>
+        <v>13.88552073979015</v>
       </c>
       <c r="P3" t="n">
-        <v>298.5028720552414</v>
+        <v>298.536664572763</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31566,28 +31627,28 @@
         <v>0.0578</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2538998312729997</v>
+        <v>-0.2542454109462343</v>
       </c>
       <c r="J4" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K4" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02845205652584049</v>
+        <v>0.02864581426804536</v>
       </c>
       <c r="M4" t="n">
-        <v>8.568254330146134</v>
+        <v>8.553117534477922</v>
       </c>
       <c r="N4" t="n">
-        <v>116.8763710053707</v>
+        <v>116.6454945838755</v>
       </c>
       <c r="O4" t="n">
-        <v>10.81093756366073</v>
+        <v>10.80025437588742</v>
       </c>
       <c r="P4" t="n">
-        <v>304.8077945143854</v>
+        <v>304.8114193670706</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31644,28 +31705,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2244581244453331</v>
+        <v>-0.2250428580935556</v>
       </c>
       <c r="J5" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K5" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02624043776612761</v>
+        <v>0.02648271122849433</v>
       </c>
       <c r="M5" t="n">
-        <v>7.647677114681398</v>
+        <v>7.636049953114345</v>
       </c>
       <c r="N5" t="n">
-        <v>99.26648378067684</v>
+        <v>99.07337834093008</v>
       </c>
       <c r="O5" t="n">
-        <v>9.963256685475731</v>
+        <v>9.953561088421072</v>
       </c>
       <c r="P5" t="n">
-        <v>304.9322457981467</v>
+        <v>304.9383791835831</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31722,28 +31783,28 @@
         <v>0.0502</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1098975826249803</v>
+        <v>-0.1116088761598177</v>
       </c>
       <c r="J6" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K6" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007019215371855791</v>
+        <v>0.007265839405410146</v>
       </c>
       <c r="M6" t="n">
-        <v>7.29031920958382</v>
+        <v>7.285554414221747</v>
       </c>
       <c r="N6" t="n">
-        <v>90.71516089561172</v>
+        <v>90.57115813892921</v>
       </c>
       <c r="O6" t="n">
-        <v>9.524450687342117</v>
+        <v>9.5168880490909</v>
       </c>
       <c r="P6" t="n">
-        <v>305.3740114415167</v>
+        <v>305.3919615336242</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31800,28 +31861,28 @@
         <v>0.0465</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08747531384470864</v>
+        <v>0.08594303966227315</v>
       </c>
       <c r="J7" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K7" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00477897029230856</v>
+        <v>0.004631879977141429</v>
       </c>
       <c r="M7" t="n">
-        <v>6.902073150811835</v>
+        <v>6.89628927290902</v>
       </c>
       <c r="N7" t="n">
-        <v>84.60724468484864</v>
+        <v>84.46817840442574</v>
       </c>
       <c r="O7" t="n">
-        <v>9.198219647564883</v>
+        <v>9.190657125822165</v>
       </c>
       <c r="P7" t="n">
-        <v>303.9104946702392</v>
+        <v>303.9265669933964</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31878,28 +31939,28 @@
         <v>0.0384</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1786540242593833</v>
+        <v>0.1755509323788335</v>
       </c>
       <c r="J8" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K8" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02126288865146753</v>
+        <v>0.02060101365675804</v>
       </c>
       <c r="M8" t="n">
-        <v>6.900359710946899</v>
+        <v>6.902532061116418</v>
       </c>
       <c r="N8" t="n">
-        <v>78.00469042427351</v>
+        <v>77.96911776395626</v>
       </c>
       <c r="O8" t="n">
-        <v>8.832026405320214</v>
+        <v>8.830012330906241</v>
       </c>
       <c r="P8" t="n">
-        <v>290.3392043071507</v>
+        <v>290.3717532439287</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31956,28 +32017,28 @@
         <v>0.054</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3201923546790388</v>
+        <v>0.3166375822107869</v>
       </c>
       <c r="J9" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K9" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08048642139711848</v>
+        <v>0.07897692151800395</v>
       </c>
       <c r="M9" t="n">
-        <v>6.256576903451534</v>
+        <v>6.263205064239106</v>
       </c>
       <c r="N9" t="n">
-        <v>62.18831139033207</v>
+        <v>62.22150506397698</v>
       </c>
       <c r="O9" t="n">
-        <v>7.885956593231545</v>
+        <v>7.888060919134499</v>
       </c>
       <c r="P9" t="n">
-        <v>288.7367045082302</v>
+        <v>288.7739912109071</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32034,28 +32095,28 @@
         <v>0.0694</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2375736770297292</v>
+        <v>0.2342970206709171</v>
       </c>
       <c r="J10" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K10" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06891057662541644</v>
+        <v>0.06721142955321646</v>
       </c>
       <c r="M10" t="n">
-        <v>4.92452037613424</v>
+        <v>4.932020283357932</v>
       </c>
       <c r="N10" t="n">
-        <v>40.49053062514255</v>
+        <v>40.54328129880144</v>
       </c>
       <c r="O10" t="n">
-        <v>6.363217002832966</v>
+        <v>6.367360622644318</v>
       </c>
       <c r="P10" t="n">
-        <v>293.051050287447</v>
+        <v>293.0854197759351</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32112,28 +32173,28 @@
         <v>0.0631</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2972269990854221</v>
+        <v>0.2939549635659616</v>
       </c>
       <c r="J11" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K11" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1004447907757774</v>
+        <v>0.09856097601056524</v>
       </c>
       <c r="M11" t="n">
-        <v>5.170122997307163</v>
+        <v>5.177299600347771</v>
       </c>
       <c r="N11" t="n">
-        <v>42.00763556878839</v>
+        <v>42.05699457145732</v>
       </c>
       <c r="O11" t="n">
-        <v>6.481329768557406</v>
+        <v>6.485136434297842</v>
       </c>
       <c r="P11" t="n">
-        <v>300.1909564579027</v>
+        <v>300.2252774775044</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32190,28 +32251,28 @@
         <v>0.0699</v>
       </c>
       <c r="I12" t="n">
-        <v>0.422611381650797</v>
+        <v>0.4177909265366596</v>
       </c>
       <c r="J12" t="n">
+        <v>503</v>
+      </c>
+      <c r="K12" t="n">
         <v>502</v>
       </c>
-      <c r="K12" t="n">
-        <v>501</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.2143476981244117</v>
+        <v>0.2098434513416043</v>
       </c>
       <c r="M12" t="n">
-        <v>4.492342916900792</v>
+        <v>4.509114015296041</v>
       </c>
       <c r="N12" t="n">
-        <v>34.81405170497987</v>
+        <v>35.03378933324466</v>
       </c>
       <c r="O12" t="n">
-        <v>5.90034335483791</v>
+        <v>5.91893481407294</v>
       </c>
       <c r="P12" t="n">
-        <v>297.7273829796923</v>
+        <v>297.7779225353859</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32268,28 +32329,28 @@
         <v>0.0607</v>
       </c>
       <c r="I13" t="n">
-        <v>0.359210757230052</v>
+        <v>0.3541325926194879</v>
       </c>
       <c r="J13" t="n">
+        <v>503</v>
+      </c>
+      <c r="K13" t="n">
         <v>502</v>
       </c>
-      <c r="K13" t="n">
-        <v>501</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1947856875961901</v>
+        <v>0.1892827171904659</v>
       </c>
       <c r="M13" t="n">
-        <v>3.978280787188899</v>
+        <v>3.9941886025111</v>
       </c>
       <c r="N13" t="n">
-        <v>28.36702158905604</v>
+        <v>28.63133844369513</v>
       </c>
       <c r="O13" t="n">
-        <v>5.326069994757489</v>
+        <v>5.35082595901746</v>
       </c>
       <c r="P13" t="n">
-        <v>294.4454900582729</v>
+        <v>294.4987315421328</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32346,28 +32407,28 @@
         <v>0.0305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3344054291475188</v>
+        <v>0.3288657132992693</v>
       </c>
       <c r="J14" t="n">
+        <v>503</v>
+      </c>
+      <c r="K14" t="n">
         <v>502</v>
       </c>
-      <c r="K14" t="n">
-        <v>501</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1335539864159552</v>
+        <v>0.1291051179726562</v>
       </c>
       <c r="M14" t="n">
-        <v>4.636918213775588</v>
+        <v>4.652520292789636</v>
       </c>
       <c r="N14" t="n">
-        <v>38.58263815662436</v>
+        <v>38.8875746199114</v>
       </c>
       <c r="O14" t="n">
-        <v>6.21149242586871</v>
+        <v>6.235990267785174</v>
       </c>
       <c r="P14" t="n">
-        <v>300.6502697731299</v>
+        <v>300.7083503424974</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32405,7 +32466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O503"/>
+  <dimension ref="A1:O504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71107,6 +71168,83 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-46.46691540524693,169.75833701489802</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-46.46753699290465,169.75788202284278</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-46.468072099081205,169.75729775774582</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-46.468583774852235,169.75670226330658</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-46.469112765562244,169.75617609138303</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-46.46969703174586,169.75572095530129</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-46.47028024482995,169.7552042729866</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>-46.47089225936349,169.7549904538672</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>-46.47147149538239,169.75476813716577</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>-46.47210395541266,169.75456645058776</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>-46.47276299715219,169.75437531739308</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>-46.47339708492125,169.7542768091784</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>-46.474011796701085,169.75428759338394</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0540/nzd0540.xlsx
+++ b/data/nzd0540/nzd0540.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O504"/>
+  <dimension ref="A1:O505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26134,14 +26134,65 @@
         <v>296.69</v>
       </c>
       <c r="M504" t="n">
-        <v>291.11</v>
+        <v>294.8</v>
       </c>
       <c r="N504" t="n">
-        <v>295.51</v>
+        <v>300.66</v>
       </c>
       <c r="O504" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>265.36</v>
+      </c>
+      <c r="C505" t="n">
+        <v>285.82</v>
+      </c>
+      <c r="D505" t="n">
+        <v>295.75</v>
+      </c>
+      <c r="E505" t="n">
+        <v>299.14</v>
+      </c>
+      <c r="F505" t="n">
+        <v>298.71</v>
+      </c>
+      <c r="G505" t="n">
+        <v>302.82</v>
+      </c>
+      <c r="H505" t="n">
+        <v>285.98</v>
+      </c>
+      <c r="I505" t="n">
+        <v>288.03</v>
+      </c>
+      <c r="J505" t="n">
+        <v>289.91</v>
+      </c>
+      <c r="K505" t="n">
+        <v>299.17</v>
+      </c>
+      <c r="L505" t="n">
+        <v>295.13</v>
+      </c>
+      <c r="M505" t="n">
+        <v>294.15</v>
+      </c>
+      <c r="N505" t="n">
+        <v>301.7</v>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26156,7 +26207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31299,6 +31350,16 @@
       </c>
       <c r="B514" t="n">
         <v>-0.8</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -31467,28 +31528,28 @@
         <v>0.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1900977060008421</v>
+        <v>0.1819329735000426</v>
       </c>
       <c r="J2" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002449896557775055</v>
+        <v>0.002251768815562105</v>
       </c>
       <c r="M2" t="n">
-        <v>20.7329468995554</v>
+        <v>20.73237426834437</v>
       </c>
       <c r="N2" t="n">
-        <v>772.9538256445893</v>
+        <v>772.2152900332313</v>
       </c>
       <c r="O2" t="n">
-        <v>27.80204714844914</v>
+        <v>27.78876193775519</v>
       </c>
       <c r="P2" t="n">
-        <v>280.543616608214</v>
+        <v>280.6305862650715</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31549,28 +31610,28 @@
         <v>0.0368</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2290225642571355</v>
+        <v>-0.2317032110788174</v>
       </c>
       <c r="J3" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K3" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01427037193351222</v>
+        <v>0.0146569846054373</v>
       </c>
       <c r="M3" t="n">
-        <v>10.8760469825422</v>
+        <v>10.86974652196713</v>
       </c>
       <c r="N3" t="n">
-        <v>192.8076862151424</v>
+        <v>192.5138468737246</v>
       </c>
       <c r="O3" t="n">
-        <v>13.88552073979015</v>
+        <v>13.8749359232295</v>
       </c>
       <c r="P3" t="n">
-        <v>298.536664572763</v>
+        <v>298.5648877142864</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31627,28 +31688,28 @@
         <v>0.0578</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2542454109462343</v>
+        <v>-0.2552021867627831</v>
       </c>
       <c r="J4" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K4" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02864581426804536</v>
+        <v>0.0289739135075392</v>
       </c>
       <c r="M4" t="n">
-        <v>8.553117534477922</v>
+        <v>8.541350422902028</v>
       </c>
       <c r="N4" t="n">
-        <v>116.6454945838755</v>
+        <v>116.4253567417691</v>
       </c>
       <c r="O4" t="n">
-        <v>10.80025437588742</v>
+        <v>10.79005823625476</v>
       </c>
       <c r="P4" t="n">
-        <v>304.8114193670706</v>
+        <v>304.8214927639308</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31705,28 +31766,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2250428580935556</v>
+        <v>-0.2250024833045184</v>
       </c>
       <c r="J5" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K5" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02648271122849433</v>
+        <v>0.02658479379580914</v>
       </c>
       <c r="M5" t="n">
-        <v>7.636049953114345</v>
+        <v>7.621052734747204</v>
       </c>
       <c r="N5" t="n">
-        <v>99.07337834093008</v>
+        <v>98.87682430280539</v>
       </c>
       <c r="O5" t="n">
-        <v>9.953561088421072</v>
+        <v>9.943682632848123</v>
       </c>
       <c r="P5" t="n">
-        <v>304.9383791835831</v>
+        <v>304.9379540983477</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31783,28 +31844,28 @@
         <v>0.0502</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1116088761598177</v>
+        <v>-0.1131077640004873</v>
       </c>
       <c r="J6" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K6" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007265839405410146</v>
+        <v>0.007490553756858476</v>
       </c>
       <c r="M6" t="n">
-        <v>7.285554414221747</v>
+        <v>7.279542852415411</v>
       </c>
       <c r="N6" t="n">
-        <v>90.57115813892921</v>
+        <v>90.4191904307895</v>
       </c>
       <c r="O6" t="n">
-        <v>9.5168880490909</v>
+        <v>9.508900590015099</v>
       </c>
       <c r="P6" t="n">
-        <v>305.3919615336242</v>
+        <v>305.4077425471143</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31861,28 +31922,28 @@
         <v>0.0465</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08594303966227315</v>
+        <v>0.08460080114417989</v>
       </c>
       <c r="J7" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K7" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004631879977141429</v>
+        <v>0.004507098266623988</v>
       </c>
       <c r="M7" t="n">
-        <v>6.89628927290902</v>
+        <v>6.88953103618385</v>
       </c>
       <c r="N7" t="n">
-        <v>84.46817840442574</v>
+        <v>84.32282513569869</v>
       </c>
       <c r="O7" t="n">
-        <v>9.190657125822165</v>
+        <v>9.182746056365639</v>
       </c>
       <c r="P7" t="n">
-        <v>303.9265669933964</v>
+        <v>303.9406987273301</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31939,28 +32000,28 @@
         <v>0.0384</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1755509323788335</v>
+        <v>0.1719570268113648</v>
       </c>
       <c r="J8" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K8" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02060101365675804</v>
+        <v>0.01982661990456058</v>
       </c>
       <c r="M8" t="n">
-        <v>6.902532061116418</v>
+        <v>6.907418278437098</v>
       </c>
       <c r="N8" t="n">
-        <v>77.96911776395626</v>
+        <v>77.97387798461232</v>
       </c>
       <c r="O8" t="n">
-        <v>8.830012330906241</v>
+        <v>8.830281874584317</v>
       </c>
       <c r="P8" t="n">
-        <v>290.3717532439287</v>
+        <v>290.4095916136208</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32017,28 +32078,28 @@
         <v>0.054</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3166375822107869</v>
+        <v>0.3130214086153683</v>
       </c>
       <c r="J9" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K9" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07897692151800395</v>
+        <v>0.07744441506358746</v>
       </c>
       <c r="M9" t="n">
-        <v>6.263205064239106</v>
+        <v>6.269987901010686</v>
       </c>
       <c r="N9" t="n">
-        <v>62.22150506397698</v>
+        <v>62.25949272544288</v>
       </c>
       <c r="O9" t="n">
-        <v>7.888060919134499</v>
+        <v>7.890468473129012</v>
       </c>
       <c r="P9" t="n">
-        <v>288.7739912109071</v>
+        <v>288.8120640291281</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32095,28 +32156,28 @@
         <v>0.0694</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2342970206709171</v>
+        <v>0.2305717915717916</v>
       </c>
       <c r="J10" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K10" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06721142955321646</v>
+        <v>0.06523469590972153</v>
       </c>
       <c r="M10" t="n">
-        <v>4.932020283357932</v>
+        <v>4.942005869961141</v>
       </c>
       <c r="N10" t="n">
-        <v>40.54328129880144</v>
+        <v>40.63416564249736</v>
       </c>
       <c r="O10" t="n">
-        <v>6.367360622644318</v>
+        <v>6.374493363593484</v>
       </c>
       <c r="P10" t="n">
-        <v>293.0854197759351</v>
+        <v>293.1246407830524</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32173,28 +32234,28 @@
         <v>0.0631</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2939549635659616</v>
+        <v>0.2904500382962267</v>
       </c>
       <c r="J11" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K11" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09856097601056524</v>
+        <v>0.09651138158758299</v>
       </c>
       <c r="M11" t="n">
-        <v>5.177299600347771</v>
+        <v>5.185608827594114</v>
       </c>
       <c r="N11" t="n">
-        <v>42.05699457145732</v>
+        <v>42.12521067789522</v>
       </c>
       <c r="O11" t="n">
-        <v>6.485136434297842</v>
+        <v>6.49039372287192</v>
       </c>
       <c r="P11" t="n">
-        <v>300.2252774775044</v>
+        <v>300.2621790197429</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32251,28 +32312,28 @@
         <v>0.0699</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4177909265366596</v>
+        <v>0.4123537663173478</v>
       </c>
       <c r="J12" t="n">
+        <v>504</v>
+      </c>
+      <c r="K12" t="n">
         <v>503</v>
       </c>
-      <c r="K12" t="n">
-        <v>502</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.2098434513416043</v>
+        <v>0.2045378921457316</v>
       </c>
       <c r="M12" t="n">
-        <v>4.509114015296041</v>
+        <v>4.529217198780825</v>
       </c>
       <c r="N12" t="n">
-        <v>35.03378933324466</v>
+        <v>35.32999796152343</v>
       </c>
       <c r="O12" t="n">
-        <v>5.91893481407294</v>
+        <v>5.943904269209207</v>
       </c>
       <c r="P12" t="n">
-        <v>297.7779225353859</v>
+        <v>297.8351420742545</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32329,28 +32390,28 @@
         <v>0.0607</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3541325926194879</v>
+        <v>0.3517453903892661</v>
       </c>
       <c r="J13" t="n">
+        <v>504</v>
+      </c>
+      <c r="K13" t="n">
         <v>503</v>
       </c>
-      <c r="K13" t="n">
-        <v>502</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1892827171904659</v>
+        <v>0.1877353029087868</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9941886025111</v>
+        <v>3.997417802730287</v>
       </c>
       <c r="N13" t="n">
-        <v>28.63133844369513</v>
+        <v>28.6000255026888</v>
       </c>
       <c r="O13" t="n">
-        <v>5.35082595901746</v>
+        <v>5.347899167214057</v>
       </c>
       <c r="P13" t="n">
-        <v>294.4987315421328</v>
+        <v>294.5239120353231</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32407,28 +32468,28 @@
         <v>0.0305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3288657132992693</v>
+        <v>0.3278535457527847</v>
       </c>
       <c r="J14" t="n">
+        <v>504</v>
+      </c>
+      <c r="K14" t="n">
         <v>503</v>
       </c>
-      <c r="K14" t="n">
-        <v>502</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1291051179726562</v>
+        <v>0.129226576406039</v>
       </c>
       <c r="M14" t="n">
-        <v>4.652520292789636</v>
+        <v>4.647695813962401</v>
       </c>
       <c r="N14" t="n">
-        <v>38.8875746199114</v>
+        <v>38.69644398622662</v>
       </c>
       <c r="O14" t="n">
-        <v>6.235990267785174</v>
+        <v>6.220646589079516</v>
       </c>
       <c r="P14" t="n">
-        <v>300.7083503424974</v>
+        <v>300.7190830744839</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32466,7 +32527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O504"/>
+  <dimension ref="A1:O505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71231,17 +71292,94 @@
       </c>
       <c r="M504" t="inlineStr">
         <is>
-          <t>-46.47339708492125,169.7542768091784</t>
+          <t>-46.47339932852158,169.75432472868792</t>
         </is>
       </c>
       <c r="N504" t="inlineStr">
         <is>
-          <t>-46.474011796701085,169.75428759338394</t>
+          <t>-46.47401550535194,169.7543544117925</t>
         </is>
       </c>
       <c r="O504" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-46.46699569923697,169.7584292603192</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-46.46754594808229,169.7578928988199</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-46.468062337826304,169.75728335718117</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-46.46859239034835,169.75671795560936</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-46.469115332616525,169.7561814341294</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-46.46969892820631,169.7557262760671</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-46.47027664915536,169.75518885856332</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>-46.47089180314606,169.75498834205186</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>-46.471467998755834,169.75475418907703</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>-46.47210251345928,169.75455906030942</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>-46.47276132917592,169.7543551565424</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>-46.47339893330889,169.75431628758156</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>-46.47401625427865,169.75436790522002</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0540/nzd0540.xlsx
+++ b/data/nzd0540/nzd0540.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O505"/>
+  <dimension ref="A1:O507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26104,7 +26104,7 @@
         <v>253.96</v>
       </c>
       <c r="C504" t="n">
-        <v>284.52</v>
+        <v>290.13</v>
       </c>
       <c r="D504" t="n">
         <v>297.3</v>
@@ -26155,7 +26155,7 @@
         <v>265.36</v>
       </c>
       <c r="C505" t="n">
-        <v>285.82</v>
+        <v>293.54</v>
       </c>
       <c r="D505" t="n">
         <v>295.75</v>
@@ -26193,6 +26193,108 @@
       <c r="O505" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>283.89</v>
+      </c>
+      <c r="C506" t="n">
+        <v>306.95</v>
+      </c>
+      <c r="D506" t="n">
+        <v>304.06</v>
+      </c>
+      <c r="E506" t="n">
+        <v>304.92</v>
+      </c>
+      <c r="F506" t="n">
+        <v>302.94</v>
+      </c>
+      <c r="G506" t="n">
+        <v>307.62</v>
+      </c>
+      <c r="H506" t="n">
+        <v>291.38</v>
+      </c>
+      <c r="I506" t="n">
+        <v>292.65</v>
+      </c>
+      <c r="J506" t="n">
+        <v>293.1</v>
+      </c>
+      <c r="K506" t="n">
+        <v>302.18</v>
+      </c>
+      <c r="L506" t="n">
+        <v>299.51</v>
+      </c>
+      <c r="M506" t="n">
+        <v>302.07</v>
+      </c>
+      <c r="N506" t="n">
+        <v>313.49</v>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>280.39</v>
+      </c>
+      <c r="C507" t="n">
+        <v>312.16</v>
+      </c>
+      <c r="D507" t="n">
+        <v>305.6</v>
+      </c>
+      <c r="E507" t="n">
+        <v>306.67</v>
+      </c>
+      <c r="F507" t="n">
+        <v>307.38</v>
+      </c>
+      <c r="G507" t="n">
+        <v>310.71</v>
+      </c>
+      <c r="H507" t="n">
+        <v>291.9</v>
+      </c>
+      <c r="I507" t="n">
+        <v>294.56</v>
+      </c>
+      <c r="J507" t="n">
+        <v>291.65</v>
+      </c>
+      <c r="K507" t="n">
+        <v>302.11</v>
+      </c>
+      <c r="L507" t="n">
+        <v>297.59</v>
+      </c>
+      <c r="M507" t="n">
+        <v>299.16</v>
+      </c>
+      <c r="N507" t="n">
+        <v>309.51</v>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26207,7 +26309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B515"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31360,6 +31462,26 @@
       </c>
       <c r="B515" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -31528,28 +31650,28 @@
         <v>0.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1819329735000426</v>
+        <v>0.1792586024762821</v>
       </c>
       <c r="J2" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K2" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002251768815562105</v>
+        <v>0.002205332754607658</v>
       </c>
       <c r="M2" t="n">
-        <v>20.73237426834437</v>
+        <v>20.66274447729801</v>
       </c>
       <c r="N2" t="n">
-        <v>772.2152900332313</v>
+        <v>769.1876044486792</v>
       </c>
       <c r="O2" t="n">
-        <v>27.78876193775519</v>
+        <v>27.73423163616903</v>
       </c>
       <c r="P2" t="n">
-        <v>280.6305862650715</v>
+        <v>280.6592852129229</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31610,28 +31732,28 @@
         <v>0.0368</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2317032110788174</v>
+        <v>-0.2127466097735788</v>
       </c>
       <c r="J3" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K3" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0146569846054373</v>
+        <v>0.01243200295267322</v>
       </c>
       <c r="M3" t="n">
-        <v>10.86974652196713</v>
+        <v>10.85825554767519</v>
       </c>
       <c r="N3" t="n">
-        <v>192.5138468737246</v>
+        <v>192.7082499201262</v>
       </c>
       <c r="O3" t="n">
-        <v>13.8749359232295</v>
+        <v>13.88193970308639</v>
       </c>
       <c r="P3" t="n">
-        <v>298.5648877142864</v>
+        <v>298.3643440083545</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31688,28 +31810,28 @@
         <v>0.0578</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2552021867627831</v>
+        <v>-0.2497926218515433</v>
       </c>
       <c r="J4" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K4" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0289739135075392</v>
+        <v>0.02798840461046082</v>
       </c>
       <c r="M4" t="n">
-        <v>8.541350422902028</v>
+        <v>8.53140107781997</v>
       </c>
       <c r="N4" t="n">
-        <v>116.4253567417691</v>
+        <v>116.1452954252064</v>
       </c>
       <c r="O4" t="n">
-        <v>10.79005823625476</v>
+        <v>10.77707267421012</v>
       </c>
       <c r="P4" t="n">
-        <v>304.8214927639308</v>
+        <v>304.7641240658499</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31766,28 +31888,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2250024833045184</v>
+        <v>-0.2195539395415405</v>
       </c>
       <c r="J5" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K5" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02658479379580914</v>
+        <v>0.02551664733862824</v>
       </c>
       <c r="M5" t="n">
-        <v>7.621052734747204</v>
+        <v>7.61128763019457</v>
       </c>
       <c r="N5" t="n">
-        <v>98.87682430280539</v>
+        <v>98.66937775917899</v>
       </c>
       <c r="O5" t="n">
-        <v>9.943682632848123</v>
+        <v>9.933246083691825</v>
       </c>
       <c r="P5" t="n">
-        <v>304.9379540983477</v>
+        <v>304.8801716290554</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31844,28 +31966,28 @@
         <v>0.0502</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1131077640004873</v>
+        <v>-0.110909320589977</v>
       </c>
       <c r="J6" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K6" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007490553756858476</v>
+        <v>0.007263455218384007</v>
       </c>
       <c r="M6" t="n">
-        <v>7.279542852415411</v>
+        <v>7.260007653979588</v>
       </c>
       <c r="N6" t="n">
-        <v>90.4191904307895</v>
+        <v>90.1106129653014</v>
       </c>
       <c r="O6" t="n">
-        <v>9.508900590015099</v>
+        <v>9.492661005497952</v>
       </c>
       <c r="P6" t="n">
-        <v>305.4077425471143</v>
+        <v>305.3844203499336</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31922,28 +32044,28 @@
         <v>0.0465</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08460080114417989</v>
+        <v>0.08700123766717266</v>
       </c>
       <c r="J7" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K7" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004507098266623988</v>
+        <v>0.004804561653600881</v>
       </c>
       <c r="M7" t="n">
-        <v>6.88953103618385</v>
+        <v>6.873562583025117</v>
       </c>
       <c r="N7" t="n">
-        <v>84.32282513569869</v>
+        <v>84.03391085195535</v>
       </c>
       <c r="O7" t="n">
-        <v>9.182746056365639</v>
+        <v>9.167001191881418</v>
       </c>
       <c r="P7" t="n">
-        <v>303.9406987273301</v>
+        <v>303.9152371999651</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32000,28 +32122,28 @@
         <v>0.0384</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1719570268113648</v>
+        <v>0.1693062975106652</v>
       </c>
       <c r="J8" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K8" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01982661990456058</v>
+        <v>0.01938756999137814</v>
       </c>
       <c r="M8" t="n">
-        <v>6.907418278437098</v>
+        <v>6.893620747010979</v>
       </c>
       <c r="N8" t="n">
-        <v>77.97387798461232</v>
+        <v>77.70864710962601</v>
       </c>
       <c r="O8" t="n">
-        <v>8.830281874584317</v>
+        <v>8.815250825111331</v>
       </c>
       <c r="P8" t="n">
-        <v>290.4095916136208</v>
+        <v>290.4377001915679</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32078,28 +32200,28 @@
         <v>0.054</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3130214086153683</v>
+        <v>0.3102423220617361</v>
       </c>
       <c r="J9" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K9" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07744441506358746</v>
+        <v>0.076742297430064</v>
       </c>
       <c r="M9" t="n">
-        <v>6.269987901010686</v>
+        <v>6.259757785240392</v>
       </c>
       <c r="N9" t="n">
-        <v>62.25949272544288</v>
+        <v>62.06393903048049</v>
       </c>
       <c r="O9" t="n">
-        <v>7.890468473129012</v>
+        <v>7.878066960268901</v>
       </c>
       <c r="P9" t="n">
-        <v>288.8120640291281</v>
+        <v>288.8415310120002</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32156,28 +32278,28 @@
         <v>0.0694</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2305717915717916</v>
+        <v>0.2250947199086217</v>
       </c>
       <c r="J10" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K10" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06523469590972153</v>
+        <v>0.06261155843905963</v>
       </c>
       <c r="M10" t="n">
-        <v>4.942005869961141</v>
+        <v>4.951550504552166</v>
       </c>
       <c r="N10" t="n">
-        <v>40.63416564249736</v>
+        <v>40.65788694599749</v>
       </c>
       <c r="O10" t="n">
-        <v>6.374493363593484</v>
+        <v>6.376353734384369</v>
       </c>
       <c r="P10" t="n">
-        <v>293.1246407830524</v>
+        <v>293.1827251837954</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32234,28 +32356,28 @@
         <v>0.0631</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2904500382962267</v>
+        <v>0.2858161580969759</v>
       </c>
       <c r="J11" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K11" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09651138158758299</v>
+        <v>0.09422623812668585</v>
       </c>
       <c r="M11" t="n">
-        <v>5.185608827594114</v>
+        <v>5.189232603422772</v>
       </c>
       <c r="N11" t="n">
-        <v>42.12521067789522</v>
+        <v>42.08918784224505</v>
       </c>
       <c r="O11" t="n">
-        <v>6.49039372287192</v>
+        <v>6.487618040717645</v>
       </c>
       <c r="P11" t="n">
-        <v>300.2621790197429</v>
+        <v>300.3113190666183</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32312,28 +32434,28 @@
         <v>0.0699</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4123537663173478</v>
+        <v>0.4042032231106648</v>
       </c>
       <c r="J12" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K12" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2045378921457316</v>
+        <v>0.1976802074842863</v>
       </c>
       <c r="M12" t="n">
-        <v>4.529217198780825</v>
+        <v>4.553997606138477</v>
       </c>
       <c r="N12" t="n">
-        <v>35.32999796152343</v>
+        <v>35.59831828761203</v>
       </c>
       <c r="O12" t="n">
-        <v>5.943904269209207</v>
+        <v>5.966432626587854</v>
       </c>
       <c r="P12" t="n">
-        <v>297.8351420742545</v>
+        <v>297.9215417023838</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32390,28 +32512,28 @@
         <v>0.0607</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3517453903892661</v>
+        <v>0.3491868961183902</v>
       </c>
       <c r="J13" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K13" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1877353029087868</v>
+        <v>0.1865915361955127</v>
       </c>
       <c r="M13" t="n">
-        <v>3.997417802730287</v>
+        <v>3.993496648309625</v>
       </c>
       <c r="N13" t="n">
-        <v>28.6000255026888</v>
+        <v>28.53502396746202</v>
       </c>
       <c r="O13" t="n">
-        <v>5.347899167214057</v>
+        <v>5.341818413935654</v>
       </c>
       <c r="P13" t="n">
-        <v>294.5239120353231</v>
+        <v>294.5510379057535</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32468,28 +32590,28 @@
         <v>0.0305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3278535457527847</v>
+        <v>0.3295551771066282</v>
       </c>
       <c r="J14" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K14" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L14" t="n">
-        <v>0.129226576406039</v>
+        <v>0.1312956105781331</v>
       </c>
       <c r="M14" t="n">
-        <v>4.647695813962401</v>
+        <v>4.638488927000778</v>
       </c>
       <c r="N14" t="n">
-        <v>38.69644398622662</v>
+        <v>38.57657845775501</v>
       </c>
       <c r="O14" t="n">
-        <v>6.220646589079516</v>
+        <v>6.211004625481695</v>
       </c>
       <c r="P14" t="n">
-        <v>300.7190830744839</v>
+        <v>300.7010537348881</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32527,7 +32649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O505"/>
+  <dimension ref="A1:O507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71242,7 +71364,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>-46.46753699290465,169.75788202284278</t>
+          <t>-46.467575637933614,169.75792895689256</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -71319,7 +71441,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>-46.46754594808229,169.7578928988199</t>
+          <t>-46.46759912804056,169.75795748546489</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -71380,6 +71502,160 @@
       <c r="O505" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-46.46712621204131,169.75857920016185</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-46.467691504027826,169.75806967577657</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-46.46811467072786,169.75736056284947</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-46.468624726412976,169.75677685273837</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-46.46913704988613,169.75622663378388</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-46.46971871734452,169.75578179712465</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-46.470292182455,169.7552554488872</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>-46.470904201512035,169.75504573375244</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>-46.471477783171615,169.75479321925982</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>-46.472109869860596,169.75459676325914</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>-46.47276601233109,169.75441176201144</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>-46.47340374878132,169.75441913922674</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>-46.47402474440438,169.75452087401226</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-46.46710156041917,169.75855087903614</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-46.46772739355249,169.75811326361324</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-46.468124368997884,169.75737487053476</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-46.4686345167383,169.756794684928</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>-46.46915984529976,169.7562740774321</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>-46.469731456588484,169.7558175388273</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>-46.470293678252226,169.75526186129088</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>-46.470909327235184,169.75506946063234</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>-46.4714733357115,169.75477547826583</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>-46.47210969878162,169.75459588644625</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>-46.472763959444585,169.75438694865377</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>-46.473401979470715,169.75438134903624</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>-46.474021878379624,169.7544692356857</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0540/nzd0540.xlsx
+++ b/data/nzd0540/nzd0540.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O507"/>
+  <dimension ref="A1:O509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26295,6 +26295,108 @@
       <c r="O507" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>272.16</v>
+      </c>
+      <c r="C508" t="n">
+        <v>309.63</v>
+      </c>
+      <c r="D508" t="n">
+        <v>304.58</v>
+      </c>
+      <c r="E508" t="n">
+        <v>306.05</v>
+      </c>
+      <c r="F508" t="n">
+        <v>306.28</v>
+      </c>
+      <c r="G508" t="n">
+        <v>309.83</v>
+      </c>
+      <c r="H508" t="n">
+        <v>289.91</v>
+      </c>
+      <c r="I508" t="n">
+        <v>293.29</v>
+      </c>
+      <c r="J508" t="n">
+        <v>291.69</v>
+      </c>
+      <c r="K508" t="n">
+        <v>301.97</v>
+      </c>
+      <c r="L508" t="n">
+        <v>298</v>
+      </c>
+      <c r="M508" t="n">
+        <v>298.63</v>
+      </c>
+      <c r="N508" t="n">
+        <v>308.22</v>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>272.12</v>
+      </c>
+      <c r="C509" t="n">
+        <v>310.62</v>
+      </c>
+      <c r="D509" t="n">
+        <v>304.8</v>
+      </c>
+      <c r="E509" t="n">
+        <v>306.05</v>
+      </c>
+      <c r="F509" t="n">
+        <v>306.85</v>
+      </c>
+      <c r="G509" t="n">
+        <v>310.98</v>
+      </c>
+      <c r="H509" t="n">
+        <v>287.17</v>
+      </c>
+      <c r="I509" t="n">
+        <v>293.13</v>
+      </c>
+      <c r="J509" t="n">
+        <v>290.47</v>
+      </c>
+      <c r="K509" t="n">
+        <v>302.25</v>
+      </c>
+      <c r="L509" t="n">
+        <v>297.55</v>
+      </c>
+      <c r="M509" t="n">
+        <v>298.21</v>
+      </c>
+      <c r="N509" t="n">
+        <v>307.99</v>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26309,7 +26411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31482,6 +31584,26 @@
       </c>
       <c r="B517" t="n">
         <v>0.38</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -31650,28 +31772,28 @@
         <v>0.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1792586024762821</v>
+        <v>0.1685516893868164</v>
       </c>
       <c r="J2" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K2" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002205332754607658</v>
+        <v>0.001965650524344498</v>
       </c>
       <c r="M2" t="n">
-        <v>20.66274447729801</v>
+        <v>20.63256703356842</v>
       </c>
       <c r="N2" t="n">
-        <v>769.1876044486792</v>
+        <v>766.8202425932506</v>
       </c>
       <c r="O2" t="n">
-        <v>27.73423163616903</v>
+        <v>27.69151932619896</v>
       </c>
       <c r="P2" t="n">
-        <v>280.6592852129229</v>
+        <v>280.7745198293583</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31732,28 +31854,28 @@
         <v>0.0368</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2127466097735788</v>
+        <v>-0.1988874591840901</v>
       </c>
       <c r="J3" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K3" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01243200295267322</v>
+        <v>0.01091056959955194</v>
       </c>
       <c r="M3" t="n">
-        <v>10.85825554767519</v>
+        <v>10.87616165247137</v>
       </c>
       <c r="N3" t="n">
-        <v>192.7082499201262</v>
+        <v>193.1265464187982</v>
       </c>
       <c r="O3" t="n">
-        <v>13.88193970308639</v>
+        <v>13.89699774839149</v>
       </c>
       <c r="P3" t="n">
-        <v>298.3643440083545</v>
+        <v>298.2169008729666</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31810,28 +31932,28 @@
         <v>0.0578</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2497926218515433</v>
+        <v>-0.2445838134762927</v>
       </c>
       <c r="J4" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K4" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02798840461046082</v>
+        <v>0.02705641887145926</v>
       </c>
       <c r="M4" t="n">
-        <v>8.53140107781997</v>
+        <v>8.520486230815427</v>
       </c>
       <c r="N4" t="n">
-        <v>116.1452954252064</v>
+        <v>115.8542061728418</v>
       </c>
       <c r="O4" t="n">
-        <v>10.77707267421012</v>
+        <v>10.76355917774608</v>
       </c>
       <c r="P4" t="n">
-        <v>304.7641240658499</v>
+        <v>304.7087097327894</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31888,28 +32010,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2195539395415405</v>
+        <v>-0.213993715968149</v>
       </c>
       <c r="J5" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K5" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02551664733862824</v>
+        <v>0.02443390388129063</v>
       </c>
       <c r="M5" t="n">
-        <v>7.61128763019457</v>
+        <v>7.602392914866315</v>
       </c>
       <c r="N5" t="n">
-        <v>98.66937775917899</v>
+        <v>98.47022186825734</v>
       </c>
       <c r="O5" t="n">
-        <v>9.933246083691825</v>
+        <v>9.923216306634524</v>
       </c>
       <c r="P5" t="n">
-        <v>304.8801716290554</v>
+        <v>304.8210196227321</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31966,28 +32088,28 @@
         <v>0.0502</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.110909320589977</v>
+        <v>-0.1076322728640442</v>
       </c>
       <c r="J6" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K6" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007263455218384007</v>
+        <v>0.006898196102292475</v>
       </c>
       <c r="M6" t="n">
-        <v>7.260007653979588</v>
+        <v>7.245044045215812</v>
       </c>
       <c r="N6" t="n">
-        <v>90.1106129653014</v>
+        <v>89.82191195889455</v>
       </c>
       <c r="O6" t="n">
-        <v>9.492661005497952</v>
+        <v>9.477442268824145</v>
       </c>
       <c r="P6" t="n">
-        <v>305.3844203499336</v>
+        <v>305.3495556213679</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32044,28 +32166,28 @@
         <v>0.0465</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08700123766717266</v>
+        <v>0.09033628650542176</v>
       </c>
       <c r="J7" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K7" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004804561653600881</v>
+        <v>0.005219030634798116</v>
       </c>
       <c r="M7" t="n">
-        <v>6.873562583025117</v>
+        <v>6.862043566610095</v>
       </c>
       <c r="N7" t="n">
-        <v>84.03391085195535</v>
+        <v>83.77243288007857</v>
       </c>
       <c r="O7" t="n">
-        <v>9.167001191881418</v>
+        <v>9.152728165966613</v>
       </c>
       <c r="P7" t="n">
-        <v>303.9152371999651</v>
+        <v>303.8797533106252</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32122,28 +32244,28 @@
         <v>0.0384</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1693062975106652</v>
+        <v>0.1642179291870356</v>
       </c>
       <c r="J8" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K8" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01938756999137814</v>
+        <v>0.01837968901429188</v>
       </c>
       <c r="M8" t="n">
-        <v>6.893620747010979</v>
+        <v>6.89211557740487</v>
       </c>
       <c r="N8" t="n">
-        <v>77.70864710962601</v>
+        <v>77.56852940835205</v>
       </c>
       <c r="O8" t="n">
-        <v>8.815250825111331</v>
+        <v>8.807299779634622</v>
       </c>
       <c r="P8" t="n">
-        <v>290.4377001915679</v>
+        <v>290.4918425484154</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32200,28 +32322,28 @@
         <v>0.054</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3102423220617361</v>
+        <v>0.3071808408290287</v>
       </c>
       <c r="J9" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K9" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L9" t="n">
-        <v>0.076742297430064</v>
+        <v>0.07589599064990493</v>
       </c>
       <c r="M9" t="n">
-        <v>6.259757785240392</v>
+        <v>6.251102695503879</v>
       </c>
       <c r="N9" t="n">
-        <v>62.06393903048049</v>
+        <v>61.8770083701037</v>
       </c>
       <c r="O9" t="n">
-        <v>7.878066960268901</v>
+        <v>7.866194020624186</v>
       </c>
       <c r="P9" t="n">
-        <v>288.8415310120002</v>
+        <v>288.8741009643456</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32278,28 +32400,28 @@
         <v>0.0694</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2250947199086217</v>
+        <v>0.2186688257058726</v>
       </c>
       <c r="J10" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K10" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06261155843905963</v>
+        <v>0.05943625405738562</v>
       </c>
       <c r="M10" t="n">
-        <v>4.951550504552166</v>
+        <v>4.966793665203064</v>
       </c>
       <c r="N10" t="n">
-        <v>40.65788694599749</v>
+        <v>40.7520619695837</v>
       </c>
       <c r="O10" t="n">
-        <v>6.376353734384369</v>
+        <v>6.383734171281234</v>
       </c>
       <c r="P10" t="n">
-        <v>293.1827251837954</v>
+        <v>293.2510910639601</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32356,28 +32478,28 @@
         <v>0.0631</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2858161580969759</v>
+        <v>0.2812222425349967</v>
       </c>
       <c r="J11" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K11" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09422623812668585</v>
+        <v>0.09196953112858741</v>
       </c>
       <c r="M11" t="n">
-        <v>5.189232603422772</v>
+        <v>5.192467723962429</v>
       </c>
       <c r="N11" t="n">
-        <v>42.08918784224505</v>
+        <v>42.05279067635729</v>
       </c>
       <c r="O11" t="n">
-        <v>6.487618040717645</v>
+        <v>6.484812308491071</v>
       </c>
       <c r="P11" t="n">
-        <v>300.3113190666183</v>
+        <v>300.3601900524878</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32434,28 +32556,28 @@
         <v>0.0699</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4042032231106648</v>
+        <v>0.3955606182106507</v>
       </c>
       <c r="J12" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K12" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1976802074842863</v>
+        <v>0.1902809350669633</v>
       </c>
       <c r="M12" t="n">
-        <v>4.553997606138477</v>
+        <v>4.580997493330233</v>
       </c>
       <c r="N12" t="n">
-        <v>35.59831828761203</v>
+        <v>35.91653000490673</v>
       </c>
       <c r="O12" t="n">
-        <v>5.966432626587854</v>
+        <v>5.993040130426855</v>
       </c>
       <c r="P12" t="n">
-        <v>297.9215417023838</v>
+        <v>298.0134491652353</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32512,28 +32634,28 @@
         <v>0.0607</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3491868961183902</v>
+        <v>0.3449007542346794</v>
       </c>
       <c r="J13" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K13" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1865915361955127</v>
+        <v>0.1835875782680784</v>
       </c>
       <c r="M13" t="n">
-        <v>3.993496648309625</v>
+        <v>3.997888660126722</v>
       </c>
       <c r="N13" t="n">
-        <v>28.53502396746202</v>
+        <v>28.53538843867405</v>
       </c>
       <c r="O13" t="n">
-        <v>5.341818413935654</v>
+        <v>5.341852528727656</v>
       </c>
       <c r="P13" t="n">
-        <v>294.5510379057535</v>
+        <v>294.5966184940864</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32590,28 +32712,28 @@
         <v>0.0305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3295551771066282</v>
+        <v>0.3285015604755946</v>
       </c>
       <c r="J14" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K14" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1312956105781331</v>
+        <v>0.131542955868245</v>
       </c>
       <c r="M14" t="n">
-        <v>4.638488927000778</v>
+        <v>4.624857908921417</v>
       </c>
       <c r="N14" t="n">
-        <v>38.57657845775501</v>
+        <v>38.43127643631588</v>
       </c>
       <c r="O14" t="n">
-        <v>6.211004625481695</v>
+        <v>6.199296446881362</v>
       </c>
       <c r="P14" t="n">
-        <v>300.7010537348881</v>
+        <v>300.7122588634377</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32649,7 +32771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O507"/>
+  <dimension ref="A1:O509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71659,6 +71781,160 @@
         </is>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-46.46704359386509,169.75848428403202</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-46.467709965435894,169.75809209715186</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-46.46811794546857,169.75736539401538</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-46.46863104816621,169.75678836723722</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>-46.46915419778912,169.75626232337137</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>-46.46972782858483,169.75580735995877</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>-46.47028795394941,169.7552373215173</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>-46.470905919032354,169.75505368412004</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>-46.47147345840009,169.75477596767254</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>-46.472109356623676,169.75459413282044</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>-46.472764397821834,169.75439224733933</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>-46.4734016572238,169.7543744662871</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>-46.47402094943697,169.75445249864157</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-46.467043312132056,169.75848396036284</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-46.46771678513413,169.75810037967864</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-46.46811933093574,169.75736743797034</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-46.46863104816621,169.75678836723722</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>-46.469157124226584,169.75626841411162</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>-46.4697325697258,169.75582066188952</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-46.47028007223761,169.75520353309423</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>-46.47090548965233,169.75505169652808</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>-46.47146971639715,169.75476104076952</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>-46.47211004093953,169.75459764007206</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>-46.47276391667606,169.75438643170884</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>-46.47340140185803,169.75436901203312</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>-46.47402078381128,169.7544495145175</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0540/nzd0540.xlsx
+++ b/data/nzd0540/nzd0540.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O509"/>
+  <dimension ref="A1:O513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26395,6 +26395,210 @@
         <v>307.99</v>
       </c>
       <c r="O509" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>278.96</v>
+      </c>
+      <c r="C510" t="n">
+        <v>310.73</v>
+      </c>
+      <c r="D510" t="n">
+        <v>306.37</v>
+      </c>
+      <c r="E510" t="n">
+        <v>306.62</v>
+      </c>
+      <c r="F510" t="n">
+        <v>307.53</v>
+      </c>
+      <c r="G510" t="n">
+        <v>311.19</v>
+      </c>
+      <c r="H510" t="n">
+        <v>289.57</v>
+      </c>
+      <c r="I510" t="n">
+        <v>293.87</v>
+      </c>
+      <c r="J510" t="n">
+        <v>291.87</v>
+      </c>
+      <c r="K510" t="n">
+        <v>302.52</v>
+      </c>
+      <c r="L510" t="n">
+        <v>298.78</v>
+      </c>
+      <c r="M510" t="n">
+        <v>299.3</v>
+      </c>
+      <c r="N510" t="n">
+        <v>308.11</v>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>280.86</v>
+      </c>
+      <c r="C511" t="n">
+        <v>308.83</v>
+      </c>
+      <c r="D511" t="n">
+        <v>305.45</v>
+      </c>
+      <c r="E511" t="n">
+        <v>306.03</v>
+      </c>
+      <c r="F511" t="n">
+        <v>306.51</v>
+      </c>
+      <c r="G511" t="n">
+        <v>309.96</v>
+      </c>
+      <c r="H511" t="n">
+        <v>289.67</v>
+      </c>
+      <c r="I511" t="n">
+        <v>293.9</v>
+      </c>
+      <c r="J511" t="n">
+        <v>292.64</v>
+      </c>
+      <c r="K511" t="n">
+        <v>302.61</v>
+      </c>
+      <c r="L511" t="n">
+        <v>299.17</v>
+      </c>
+      <c r="M511" t="n">
+        <v>299.63</v>
+      </c>
+      <c r="N511" t="n">
+        <v>307.4</v>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>282.57</v>
+      </c>
+      <c r="C512" t="n">
+        <v>308.44</v>
+      </c>
+      <c r="D512" t="n">
+        <v>306.52</v>
+      </c>
+      <c r="E512" t="n">
+        <v>306.7</v>
+      </c>
+      <c r="F512" t="n">
+        <v>306.84</v>
+      </c>
+      <c r="G512" t="n">
+        <v>310.43</v>
+      </c>
+      <c r="H512" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="I512" t="n">
+        <v>295.1</v>
+      </c>
+      <c r="J512" t="n">
+        <v>293.84</v>
+      </c>
+      <c r="K512" t="n">
+        <v>303.79</v>
+      </c>
+      <c r="L512" t="n">
+        <v>300.66</v>
+      </c>
+      <c r="M512" t="n">
+        <v>300.96</v>
+      </c>
+      <c r="N512" t="n">
+        <v>308.41</v>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="C513" t="n">
+        <v>310.47</v>
+      </c>
+      <c r="D513" t="n">
+        <v>308.35</v>
+      </c>
+      <c r="E513" t="n">
+        <v>308.51</v>
+      </c>
+      <c r="F513" t="n">
+        <v>307.26</v>
+      </c>
+      <c r="G513" t="n">
+        <v>310.9</v>
+      </c>
+      <c r="H513" t="n">
+        <v>292.7</v>
+      </c>
+      <c r="I513" t="n">
+        <v>296.13</v>
+      </c>
+      <c r="J513" t="n">
+        <v>295.58</v>
+      </c>
+      <c r="K513" t="n">
+        <v>305.92</v>
+      </c>
+      <c r="L513" t="n">
+        <v>303.72</v>
+      </c>
+      <c r="M513" t="n">
+        <v>303.42</v>
+      </c>
+      <c r="N513" t="n">
+        <v>309.92</v>
+      </c>
+      <c r="O513" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -26411,7 +26615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B519"/>
+  <dimension ref="A1:B523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31604,6 +31808,46 @@
       </c>
       <c r="B519" t="n">
         <v>0.4</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>-0.26</v>
       </c>
     </row>
   </sheetData>
@@ -31772,28 +32016,28 @@
         <v>0.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1685516893868164</v>
+        <v>0.160983769759215</v>
       </c>
       <c r="J2" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K2" t="n">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001965650524344498</v>
+        <v>0.001824288634764915</v>
       </c>
       <c r="M2" t="n">
-        <v>20.63256703356842</v>
+        <v>20.50595266749981</v>
       </c>
       <c r="N2" t="n">
-        <v>766.8202425932506</v>
+        <v>760.9613008157387</v>
       </c>
       <c r="O2" t="n">
-        <v>27.69151932619896</v>
+        <v>27.5855270171831</v>
       </c>
       <c r="P2" t="n">
-        <v>280.7745198293583</v>
+        <v>280.8562164047685</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31854,28 +32098,28 @@
         <v>0.0368</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1988874591840901</v>
+        <v>-0.1727962903172997</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K3" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01091056959955194</v>
+        <v>0.008309284146839513</v>
       </c>
       <c r="M3" t="n">
-        <v>10.87616165247137</v>
+        <v>10.90732399703069</v>
       </c>
       <c r="N3" t="n">
-        <v>193.1265464187982</v>
+        <v>193.7453142843379</v>
       </c>
       <c r="O3" t="n">
-        <v>13.89699774839149</v>
+        <v>13.91924259018205</v>
       </c>
       <c r="P3" t="n">
-        <v>298.2169008729666</v>
+        <v>297.9384932524843</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31932,28 +32176,28 @@
         <v>0.0578</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2445838134762927</v>
+        <v>-0.2313556510449659</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K4" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02705641887145926</v>
+        <v>0.02457605439620958</v>
       </c>
       <c r="M4" t="n">
-        <v>8.520486230815427</v>
+        <v>8.510855041962291</v>
       </c>
       <c r="N4" t="n">
-        <v>115.8542061728418</v>
+        <v>115.5024559965965</v>
       </c>
       <c r="O4" t="n">
-        <v>10.76355917774608</v>
+        <v>10.74720689279761</v>
       </c>
       <c r="P4" t="n">
-        <v>304.7087097327894</v>
+        <v>304.5675446876843</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32010,28 +32254,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.213993715968149</v>
+        <v>-0.2017485035086282</v>
       </c>
       <c r="J5" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K5" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02443390388129063</v>
+        <v>0.02204404057530285</v>
       </c>
       <c r="M5" t="n">
-        <v>7.602392914866315</v>
+        <v>7.590081348514645</v>
       </c>
       <c r="N5" t="n">
-        <v>98.47022186825734</v>
+        <v>98.17445105653727</v>
       </c>
       <c r="O5" t="n">
-        <v>9.923216306634524</v>
+        <v>9.908302127838919</v>
       </c>
       <c r="P5" t="n">
-        <v>304.8210196227321</v>
+        <v>304.6903440857042</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32088,28 +32332,28 @@
         <v>0.0502</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1076322728640442</v>
+        <v>-0.1005261271904239</v>
       </c>
       <c r="J6" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K6" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006898196102292475</v>
+        <v>0.006116396443543226</v>
       </c>
       <c r="M6" t="n">
-        <v>7.245044045215812</v>
+        <v>7.217686221787202</v>
       </c>
       <c r="N6" t="n">
-        <v>89.82191195889455</v>
+        <v>89.27863542770636</v>
       </c>
       <c r="O6" t="n">
-        <v>9.477442268824145</v>
+        <v>9.448737239848844</v>
       </c>
       <c r="P6" t="n">
-        <v>305.3495556213679</v>
+        <v>305.2737296314662</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32166,28 +32410,28 @@
         <v>0.0465</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09033628650542176</v>
+        <v>0.09712865176673653</v>
       </c>
       <c r="J7" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K7" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005219030634798116</v>
+        <v>0.006122425602457904</v>
       </c>
       <c r="M7" t="n">
-        <v>6.862043566610095</v>
+        <v>6.839923964487101</v>
       </c>
       <c r="N7" t="n">
-        <v>83.77243288007857</v>
+        <v>83.26334182389638</v>
       </c>
       <c r="O7" t="n">
-        <v>9.152728165966613</v>
+        <v>9.124874893602453</v>
       </c>
       <c r="P7" t="n">
-        <v>303.8797533106252</v>
+        <v>303.8072753810197</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32244,28 +32488,28 @@
         <v>0.0384</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1642179291870356</v>
+        <v>0.157803146320552</v>
       </c>
       <c r="J8" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K8" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01837968901429188</v>
+        <v>0.01725631383880744</v>
       </c>
       <c r="M8" t="n">
-        <v>6.89211557740487</v>
+        <v>6.870247716630351</v>
       </c>
       <c r="N8" t="n">
-        <v>77.56852940835205</v>
+        <v>77.10335742245287</v>
       </c>
       <c r="O8" t="n">
-        <v>8.807299779634622</v>
+        <v>8.780851748119478</v>
       </c>
       <c r="P8" t="n">
-        <v>290.4918425484154</v>
+        <v>290.5602718611531</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32322,28 +32566,28 @@
         <v>0.054</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3071808408290287</v>
+        <v>0.3036154181413772</v>
       </c>
       <c r="J9" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K9" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07589599064990493</v>
+        <v>0.07542058746849523</v>
       </c>
       <c r="M9" t="n">
-        <v>6.251102695503879</v>
+        <v>6.220895772356371</v>
       </c>
       <c r="N9" t="n">
-        <v>61.8770083701037</v>
+        <v>61.44006887507611</v>
       </c>
       <c r="O9" t="n">
-        <v>7.866194020624186</v>
+        <v>7.838371570363076</v>
       </c>
       <c r="P9" t="n">
-        <v>288.8741009643456</v>
+        <v>288.912131751428</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32400,28 +32644,28 @@
         <v>0.0694</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2186688257058726</v>
+        <v>0.2099550861017858</v>
       </c>
       <c r="J10" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K10" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05943625405738562</v>
+        <v>0.05562940197395327</v>
       </c>
       <c r="M10" t="n">
-        <v>4.966793665203064</v>
+        <v>4.975707382370102</v>
       </c>
       <c r="N10" t="n">
-        <v>40.7520619695837</v>
+        <v>40.68558898727493</v>
       </c>
       <c r="O10" t="n">
-        <v>6.383734171281234</v>
+        <v>6.378525612339809</v>
       </c>
       <c r="P10" t="n">
-        <v>293.2510910639601</v>
+        <v>293.3440487061973</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32478,28 +32722,28 @@
         <v>0.0631</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2812222425349967</v>
+        <v>0.2747863911985793</v>
       </c>
       <c r="J11" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K11" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09196953112858741</v>
+        <v>0.0892966347937354</v>
       </c>
       <c r="M11" t="n">
-        <v>5.192467723962429</v>
+        <v>5.184830367044225</v>
       </c>
       <c r="N11" t="n">
-        <v>42.05279067635729</v>
+        <v>41.86798227818667</v>
       </c>
       <c r="O11" t="n">
-        <v>6.484812308491071</v>
+        <v>6.47054729355923</v>
       </c>
       <c r="P11" t="n">
-        <v>300.3601900524878</v>
+        <v>300.4288422523642</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32556,28 +32800,28 @@
         <v>0.0699</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3955606182106507</v>
+        <v>0.3831585928066623</v>
       </c>
       <c r="J12" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K12" t="n">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1902809350669633</v>
+        <v>0.1811156596878541</v>
       </c>
       <c r="M12" t="n">
-        <v>4.580997493330233</v>
+        <v>4.609495147625791</v>
       </c>
       <c r="N12" t="n">
-        <v>35.91653000490673</v>
+        <v>36.14522940709497</v>
       </c>
       <c r="O12" t="n">
-        <v>5.993040130426855</v>
+        <v>6.012090269373454</v>
       </c>
       <c r="P12" t="n">
-        <v>298.0134491652353</v>
+        <v>298.1457005835781</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32634,28 +32878,28 @@
         <v>0.0607</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3449007542346794</v>
+        <v>0.3403287657264273</v>
       </c>
       <c r="J13" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K13" t="n">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1835875782680784</v>
+        <v>0.1817338879061179</v>
       </c>
       <c r="M13" t="n">
-        <v>3.997888660126722</v>
+        <v>3.987904828515518</v>
       </c>
       <c r="N13" t="n">
-        <v>28.53538843867405</v>
+        <v>28.39770526673498</v>
       </c>
       <c r="O13" t="n">
-        <v>5.341852528727656</v>
+        <v>5.328949733928344</v>
       </c>
       <c r="P13" t="n">
-        <v>294.5966184940864</v>
+        <v>294.6453585606969</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32712,28 +32956,28 @@
         <v>0.0305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3285015604755946</v>
+        <v>0.3269772113075848</v>
       </c>
       <c r="J14" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K14" t="n">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="L14" t="n">
-        <v>0.131542955868245</v>
+        <v>0.1324170657480525</v>
       </c>
       <c r="M14" t="n">
-        <v>4.624857908921417</v>
+        <v>4.597271213532548</v>
       </c>
       <c r="N14" t="n">
-        <v>38.43127643631588</v>
+        <v>38.14426878012748</v>
       </c>
       <c r="O14" t="n">
-        <v>6.199296446881362</v>
+        <v>6.176104660716776</v>
       </c>
       <c r="P14" t="n">
-        <v>300.7122588634377</v>
+        <v>300.72850524778</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32771,7 +33015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O509"/>
+  <dimension ref="A1:O513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71935,6 +72179,314 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-46.467091488468846,169.75853930784064</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-46.46771754287833,169.75810129995952</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-46.46812921813226,169.7573820243793</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-46.46863423701475,169.75679417543677</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-46.46916061541475,169.75627568025877</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-46.46973343549921,169.755823090938</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-46.47028697592731,169.75523312879272</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-46.47090747553471,169.75506088914113</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>-46.471474010498724,169.75477817000268</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>-46.47211070081544,169.75460102206478</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>-46.472765231807166,169.75440232776583</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>-46.47340206459248,169.75438316712092</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>-46.474020870224685,169.7544510714518</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-46.467104870780226,169.75855468215727</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-46.46770445456825,169.75808540420243</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-46.46812342436125,169.75737347692882</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-46.46863093627677,169.75678816344077</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-46.46915537863235,169.7562647810384</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-46.469728364539975,169.75580886365518</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-46.47028726358087,169.75523436194698</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-46.470907556043436,169.75506126181466</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>-46.47147637225352,169.7547875910821</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>-46.472110920774064,169.7546021493957</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-46.47276564879951,169.7544073679792</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>-46.4734022652365,169.7543874526063</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>-46.47402035894503,169.75444185959063</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-46.46711691485886,169.7585685190486</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-46.46770176802013,169.75808214139005</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-46.46813016276878,169.75738341798552</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-46.46863468457242,169.75679499062272</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-46.469157072885594,169.75626830725653</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-46.469730302223795,169.75581430009626</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-46.470291233198886,169.7552513794774</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-46.470910776391634,169.75507616875632</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-46.471480052908845,169.75480227328552</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>-46.472113804674876,169.75461692995762</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-46.47276724192203,169.75442662417984</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>-46.47340307389111,169.75440472441144</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>-46.47402108625814,169.75445496378757</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-46.46709529186279,169.7585436773825</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-46.467715751846555,169.7580991247502</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-46.46814168733302,169.7574004199854</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-46.468644810563205,169.75681343420862</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-46.46915922920774,169.7562727951708</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-46.46973223990735,169.75581973653775</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-46.47029597947804,169.75527172652798</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-46.47091354052232,169.7550889638827</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-46.47148538985578,169.75482356248415</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-46.47211901035551,169.75464361012868</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-46.472770513693774,169.75446617047513</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>-46.473404569591295,169.75443667075947</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>-46.474022173624455,169.7544745552115</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0540/nzd0540.xlsx
+++ b/data/nzd0540/nzd0540.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O513"/>
+  <dimension ref="A1:O514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26601,6 +26601,57 @@
       <c r="O513" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>273.42</v>
+      </c>
+      <c r="C514" t="n">
+        <v>303.9</v>
+      </c>
+      <c r="D514" t="n">
+        <v>308.35</v>
+      </c>
+      <c r="E514" t="n">
+        <v>305.57</v>
+      </c>
+      <c r="F514" t="n">
+        <v>305.21</v>
+      </c>
+      <c r="G514" t="n">
+        <v>304.94</v>
+      </c>
+      <c r="H514" t="n">
+        <v>291.46</v>
+      </c>
+      <c r="I514" t="n">
+        <v>292.09</v>
+      </c>
+      <c r="J514" t="n">
+        <v>291.87</v>
+      </c>
+      <c r="K514" t="n">
+        <v>303.12</v>
+      </c>
+      <c r="L514" t="n">
+        <v>300.72</v>
+      </c>
+      <c r="M514" t="n">
+        <v>298.73</v>
+      </c>
+      <c r="N514" t="n">
+        <v>303.2</v>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26615,7 +26666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B523"/>
+  <dimension ref="A1:B524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31848,6 +31899,16 @@
       </c>
       <c r="B523" t="n">
         <v>-0.26</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -32016,28 +32077,28 @@
         <v>0.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.160983769759215</v>
+        <v>0.1563238418708315</v>
       </c>
       <c r="J2" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K2" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001824288634764915</v>
+        <v>0.001727225494736362</v>
       </c>
       <c r="M2" t="n">
-        <v>20.50595266749981</v>
+        <v>20.48756105539616</v>
       </c>
       <c r="N2" t="n">
-        <v>760.9613008157387</v>
+        <v>759.7324693763061</v>
       </c>
       <c r="O2" t="n">
-        <v>27.5855270171831</v>
+        <v>27.56324489925499</v>
       </c>
       <c r="P2" t="n">
-        <v>280.8562164047685</v>
+        <v>280.9067389864961</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32098,28 +32159,28 @@
         <v>0.0368</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1727962903172997</v>
+        <v>-0.1686528458175405</v>
       </c>
       <c r="J3" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K3" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008309284146839513</v>
+        <v>0.007943881165432654</v>
       </c>
       <c r="M3" t="n">
-        <v>10.90732399703069</v>
+        <v>10.90465165798459</v>
       </c>
       <c r="N3" t="n">
-        <v>193.7453142843379</v>
+        <v>193.5837944899284</v>
       </c>
       <c r="O3" t="n">
-        <v>13.91924259018205</v>
+        <v>13.91343934798037</v>
       </c>
       <c r="P3" t="n">
-        <v>297.9384932524843</v>
+        <v>297.8940873391868</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32176,28 +32237,28 @@
         <v>0.0578</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2313556510449659</v>
+        <v>-0.227454722592613</v>
       </c>
       <c r="J4" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K4" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02457605439620958</v>
+        <v>0.0238355965812943</v>
       </c>
       <c r="M4" t="n">
-        <v>8.510855041962291</v>
+        <v>8.511020212608125</v>
       </c>
       <c r="N4" t="n">
-        <v>115.5024559965965</v>
+        <v>115.4688941721263</v>
       </c>
       <c r="O4" t="n">
-        <v>10.74720689279761</v>
+        <v>10.74564535856857</v>
       </c>
       <c r="P4" t="n">
-        <v>304.5675446876843</v>
+        <v>304.5257378550733</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32254,28 +32315,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2017485035086282</v>
+        <v>-0.1992958255439404</v>
       </c>
       <c r="J5" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K5" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02204404057530285</v>
+        <v>0.02159759626336233</v>
       </c>
       <c r="M5" t="n">
-        <v>7.590081348514645</v>
+        <v>7.584673541378006</v>
       </c>
       <c r="N5" t="n">
-        <v>98.17445105653727</v>
+        <v>98.05881624017879</v>
       </c>
       <c r="O5" t="n">
-        <v>9.908302127838919</v>
+        <v>9.902465159755867</v>
       </c>
       <c r="P5" t="n">
-        <v>304.6903440857042</v>
+        <v>304.6640583697852</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32332,28 +32393,28 @@
         <v>0.0502</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1005261271904239</v>
+        <v>-0.09949937885191849</v>
       </c>
       <c r="J6" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K6" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006116396443543226</v>
+        <v>0.006017730027362389</v>
       </c>
       <c r="M6" t="n">
-        <v>7.217686221787202</v>
+        <v>7.207823924961784</v>
       </c>
       <c r="N6" t="n">
-        <v>89.27863542770636</v>
+        <v>89.11787581326431</v>
       </c>
       <c r="O6" t="n">
-        <v>9.448737239848844</v>
+        <v>9.440226470443614</v>
       </c>
       <c r="P6" t="n">
-        <v>305.2737296314662</v>
+        <v>305.2627258162346</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32410,28 +32471,28 @@
         <v>0.0465</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09712865176673653</v>
+        <v>0.09655869654762492</v>
       </c>
       <c r="J7" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K7" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006122425602457904</v>
+        <v>0.006076953206883839</v>
       </c>
       <c r="M7" t="n">
-        <v>6.839923964487101</v>
+        <v>6.829580872371726</v>
       </c>
       <c r="N7" t="n">
-        <v>83.26334182389638</v>
+        <v>83.10512504998496</v>
       </c>
       <c r="O7" t="n">
-        <v>9.124874893602453</v>
+        <v>9.116201240099132</v>
       </c>
       <c r="P7" t="n">
-        <v>303.8072753810197</v>
+        <v>303.8133836761941</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32488,28 +32549,28 @@
         <v>0.0384</v>
       </c>
       <c r="I8" t="n">
-        <v>0.157803146320552</v>
+        <v>0.1565054216184233</v>
       </c>
       <c r="J8" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K8" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01725631383880744</v>
+        <v>0.01704608108897099</v>
       </c>
       <c r="M8" t="n">
-        <v>6.870247716630351</v>
+        <v>6.863263858058995</v>
       </c>
       <c r="N8" t="n">
-        <v>77.10335742245287</v>
+        <v>76.97426161668233</v>
       </c>
       <c r="O8" t="n">
-        <v>8.780851748119478</v>
+        <v>8.773497684315094</v>
       </c>
       <c r="P8" t="n">
-        <v>290.5602718611531</v>
+        <v>290.574179770529</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32566,28 +32627,28 @@
         <v>0.054</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3036154181413772</v>
+        <v>0.30168657646166</v>
       </c>
       <c r="J9" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K9" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07542058746849523</v>
+        <v>0.07478219265099784</v>
       </c>
       <c r="M9" t="n">
-        <v>6.220895772356371</v>
+        <v>6.218773752456517</v>
       </c>
       <c r="N9" t="n">
-        <v>61.44006887507611</v>
+        <v>61.3671438718071</v>
       </c>
       <c r="O9" t="n">
-        <v>7.838371570363076</v>
+        <v>7.833718393700855</v>
       </c>
       <c r="P9" t="n">
-        <v>288.912131751428</v>
+        <v>288.9328034356751</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32644,28 +32705,28 @@
         <v>0.0694</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2099550861017858</v>
+        <v>0.2071803233155857</v>
       </c>
       <c r="J10" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K10" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05562940197395327</v>
+        <v>0.05434731532561132</v>
       </c>
       <c r="M10" t="n">
-        <v>4.975707382370102</v>
+        <v>4.981054660046303</v>
       </c>
       <c r="N10" t="n">
-        <v>40.68558898727493</v>
+        <v>40.70321620307099</v>
       </c>
       <c r="O10" t="n">
-        <v>6.378525612339809</v>
+        <v>6.37990722527146</v>
       </c>
       <c r="P10" t="n">
-        <v>293.3440487061973</v>
+        <v>293.373786253234</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32722,28 +32783,28 @@
         <v>0.0631</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2747863911985793</v>
+        <v>0.2729699952079283</v>
       </c>
       <c r="J11" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K11" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0892966347937354</v>
+        <v>0.08849168631870941</v>
       </c>
       <c r="M11" t="n">
-        <v>5.184830367044225</v>
+        <v>5.184124782856063</v>
       </c>
       <c r="N11" t="n">
-        <v>41.86798227818667</v>
+        <v>41.82790727762002</v>
       </c>
       <c r="O11" t="n">
-        <v>6.47054729355923</v>
+        <v>6.467449827994031</v>
       </c>
       <c r="P11" t="n">
-        <v>300.4288422523642</v>
+        <v>300.4483088393739</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32800,28 +32861,28 @@
         <v>0.0699</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3831585928066623</v>
+        <v>0.3801639554666916</v>
       </c>
       <c r="J12" t="n">
+        <v>513</v>
+      </c>
+      <c r="K12" t="n">
         <v>512</v>
       </c>
-      <c r="K12" t="n">
-        <v>511</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1811156596878541</v>
+        <v>0.1789737120077506</v>
       </c>
       <c r="M12" t="n">
-        <v>4.609495147625791</v>
+        <v>4.616002037894851</v>
       </c>
       <c r="N12" t="n">
-        <v>36.14522940709497</v>
+        <v>36.18780565402531</v>
       </c>
       <c r="O12" t="n">
-        <v>6.012090269373454</v>
+        <v>6.015630112799931</v>
       </c>
       <c r="P12" t="n">
-        <v>298.1457005835781</v>
+        <v>298.1777820738066</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32878,28 +32939,28 @@
         <v>0.0607</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3403287657264273</v>
+        <v>0.3383713797122569</v>
       </c>
       <c r="J13" t="n">
+        <v>513</v>
+      </c>
+      <c r="K13" t="n">
         <v>512</v>
       </c>
-      <c r="K13" t="n">
-        <v>511</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1817338879061179</v>
+        <v>0.1804104759334136</v>
       </c>
       <c r="M13" t="n">
-        <v>3.987904828515518</v>
+        <v>3.989203624759946</v>
       </c>
       <c r="N13" t="n">
-        <v>28.39770526673498</v>
+        <v>28.39059194840881</v>
       </c>
       <c r="O13" t="n">
-        <v>5.328949733928344</v>
+        <v>5.328282269963633</v>
       </c>
       <c r="P13" t="n">
-        <v>294.6453585606969</v>
+        <v>294.6663279981138</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32956,28 +33017,28 @@
         <v>0.0305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3269772113075848</v>
+        <v>0.3245302808830422</v>
       </c>
       <c r="J14" t="n">
+        <v>513</v>
+      </c>
+      <c r="K14" t="n">
         <v>512</v>
       </c>
-      <c r="K14" t="n">
-        <v>511</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1324170657480525</v>
+        <v>0.1309659606206452</v>
       </c>
       <c r="M14" t="n">
-        <v>4.597271213532548</v>
+        <v>4.599051143174461</v>
       </c>
       <c r="N14" t="n">
-        <v>38.14426878012748</v>
+        <v>38.14532883631607</v>
       </c>
       <c r="O14" t="n">
-        <v>6.176104660716776</v>
+        <v>6.176190479277341</v>
       </c>
       <c r="P14" t="n">
-        <v>300.72850524778</v>
+        <v>300.7547191647231</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33015,7 +33076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O513"/>
+  <dimension ref="A1:O514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72487,6 +72548,83 @@
         </is>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-46.46705246845527,169.75849447961286</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-46.46767049383831,169.75804415893126</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-46.46814168733302,169.7574004199854</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-46.468628362819835,169.7567834761223</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-46.46914870430039,169.7562508898783</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-46.46970766841224,169.75575079786242</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-46.47029241257768,169.75525643541081</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-46.47090269868129,169.7550387771812</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-46.471474010498724,169.75477817000268</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>-46.47211216720599,169.75460853760447</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-46.47276730607454,169.75442739959732</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>-46.473401718025144,169.754375764919</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>-46.47401733445864,169.75438736689517</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
